--- a/Cell data Sara DU145/2026_03_11/2026_03_11.xlsx
+++ b/Cell data Sara DU145/2026_03_11/2026_03_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{086FB7D2-E0DF-4D79-B0DE-186A3ECB94C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673814F5-82B8-46A4-9D59-6D2AE46EFE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,9 +27,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="8">
   <si>
-    <t>Radiation</t>
-  </si>
-  <si>
     <t>Experiment</t>
   </si>
   <si>
@@ -39,16 +36,19 @@
     <t>Dose</t>
   </si>
   <si>
-    <t>Flask number</t>
-  </si>
-  <si>
     <t>Cells plated</t>
   </si>
   <si>
-    <t>Colonies</t>
+    <t>X-ray</t>
   </si>
   <si>
-    <t>X-ray</t>
+    <t>Rad</t>
+  </si>
+  <si>
+    <t>Triplicate</t>
+  </si>
+  <si>
+    <t>Count</t>
   </si>
 </sst>
 </file>
@@ -532,8 +532,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
@@ -860,370 +859,370 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>6</v>
+      </c>
+      <c r="F1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2">
+        <v>6</v>
+      </c>
+      <c r="C2">
+        <v>2</v>
+      </c>
+      <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>1</v>
+      </c>
+      <c r="F2">
+        <v>250</v>
+      </c>
+      <c r="G2">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>4</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="D3">
+        <v>0</v>
+      </c>
+      <c r="E3">
+        <v>2</v>
+      </c>
+      <c r="F3">
+        <v>250</v>
+      </c>
+      <c r="G3">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>4</v>
+      </c>
+      <c r="B4">
+        <v>6</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+      <c r="D4">
+        <v>0</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>250</v>
+      </c>
+      <c r="G4">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>6</v>
+      </c>
+      <c r="C5">
+        <v>2</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5">
+        <v>4</v>
+      </c>
+      <c r="F5">
+        <v>250</v>
+      </c>
+      <c r="G5">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6">
+        <v>6</v>
+      </c>
+      <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B2" s="1">
-        <v>6</v>
-      </c>
-      <c r="C2" s="1">
-        <v>2</v>
-      </c>
-      <c r="D2" s="1">
+      <c r="F6">
+        <v>250</v>
+      </c>
+      <c r="G6">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>6</v>
+      </c>
+      <c r="C7">
+        <v>2</v>
+      </c>
+      <c r="D7">
         <v>0</v>
       </c>
-      <c r="E2" s="1">
+      <c r="E7">
+        <v>6</v>
+      </c>
+      <c r="F7">
+        <v>250</v>
+      </c>
+      <c r="G7">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>4</v>
+      </c>
+      <c r="B8">
+        <v>6</v>
+      </c>
+      <c r="C8">
+        <v>2</v>
+      </c>
+      <c r="D8">
+        <v>1.7</v>
+      </c>
+      <c r="E8">
         <v>1</v>
       </c>
-      <c r="F2" s="1">
-        <v>250</v>
-      </c>
-      <c r="G2" s="1">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B3" s="1">
-        <v>6</v>
-      </c>
-      <c r="C3" s="1">
-        <v>2</v>
-      </c>
-      <c r="D3" s="1">
-        <v>0</v>
-      </c>
-      <c r="E3" s="1">
-        <v>2</v>
-      </c>
-      <c r="F3" s="1">
-        <v>250</v>
-      </c>
-      <c r="G3" s="1">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="1">
-        <v>6</v>
-      </c>
-      <c r="C4" s="1">
-        <v>2</v>
-      </c>
-      <c r="D4" s="1">
-        <v>0</v>
-      </c>
-      <c r="E4" s="1">
+      <c r="F8">
+        <v>500</v>
+      </c>
+      <c r="G8">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9">
+        <v>6</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+      <c r="D9">
+        <v>1.7</v>
+      </c>
+      <c r="E9">
+        <v>2</v>
+      </c>
+      <c r="F9">
+        <v>500</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10">
+        <v>6</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10">
+        <v>1.7</v>
+      </c>
+      <c r="E10">
         <v>3</v>
       </c>
-      <c r="F4" s="1">
-        <v>250</v>
-      </c>
-      <c r="G4" s="1">
+      <c r="F10">
+        <v>500</v>
+      </c>
+      <c r="G10">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>4</v>
+      </c>
+      <c r="B11">
+        <v>6</v>
+      </c>
+      <c r="C11">
+        <v>2</v>
+      </c>
+      <c r="D11">
+        <v>4.25</v>
+      </c>
+      <c r="E11">
+        <v>1</v>
+      </c>
+      <c r="F11">
+        <v>1600</v>
+      </c>
+      <c r="G11">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>2</v>
+      </c>
+      <c r="D12">
+        <v>4.25</v>
+      </c>
+      <c r="E12">
+        <v>2</v>
+      </c>
+      <c r="F12">
+        <v>1600</v>
+      </c>
+      <c r="G12">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" t="s">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+      <c r="C13">
+        <v>2</v>
+      </c>
+      <c r="D13">
+        <v>4.25</v>
+      </c>
+      <c r="E13">
+        <v>3</v>
+      </c>
+      <c r="F13">
+        <v>1600</v>
+      </c>
+      <c r="G13">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" t="s">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>6</v>
+      </c>
+      <c r="C14">
+        <v>2</v>
+      </c>
+      <c r="D14">
+        <v>6.8</v>
+      </c>
+      <c r="E14">
+        <v>1</v>
+      </c>
+      <c r="F14">
+        <v>4000</v>
+      </c>
+      <c r="G14">
         <v>23</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B5" s="1">
-        <v>6</v>
-      </c>
-      <c r="C5" s="1">
-        <v>2</v>
-      </c>
-      <c r="D5" s="1">
-        <v>0</v>
-      </c>
-      <c r="E5" s="1">
-        <v>4</v>
-      </c>
-      <c r="F5" s="1">
-        <v>250</v>
-      </c>
-      <c r="G5" s="1">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B6" s="1">
-        <v>6</v>
-      </c>
-      <c r="C6" s="1">
-        <v>2</v>
-      </c>
-      <c r="D6" s="1">
-        <v>0</v>
-      </c>
-      <c r="E6" s="1">
-        <v>5</v>
-      </c>
-      <c r="F6" s="1">
-        <v>250</v>
-      </c>
-      <c r="G6" s="1">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="1">
-        <v>6</v>
-      </c>
-      <c r="C7" s="1">
-        <v>2</v>
-      </c>
-      <c r="D7" s="1">
-        <v>0</v>
-      </c>
-      <c r="E7" s="1">
-        <v>6</v>
-      </c>
-      <c r="F7" s="1">
-        <v>250</v>
-      </c>
-      <c r="G7" s="1">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1">
-        <v>6</v>
-      </c>
-      <c r="C8" s="1">
-        <v>2</v>
-      </c>
-      <c r="D8" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="E8" s="1">
-        <v>1</v>
-      </c>
-      <c r="F8" s="1">
-        <v>500</v>
-      </c>
-      <c r="G8" s="1">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="1">
-        <v>6</v>
-      </c>
-      <c r="C9" s="1">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="E9" s="1">
-        <v>2</v>
-      </c>
-      <c r="F9" s="1">
-        <v>500</v>
-      </c>
-      <c r="G9" s="1">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="1">
-        <v>6</v>
-      </c>
-      <c r="C10" s="1">
-        <v>2</v>
-      </c>
-      <c r="D10" s="1">
-        <v>1.7</v>
-      </c>
-      <c r="E10" s="1">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" t="s">
+        <v>4</v>
+      </c>
+      <c r="B15">
+        <v>6</v>
+      </c>
+      <c r="C15">
+        <v>2</v>
+      </c>
+      <c r="D15">
+        <v>6.8</v>
+      </c>
+      <c r="E15">
+        <v>2</v>
+      </c>
+      <c r="F15">
+        <v>4000</v>
+      </c>
+      <c r="G15">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" t="s">
+        <v>4</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+      <c r="C16">
+        <v>2</v>
+      </c>
+      <c r="D16">
+        <v>6.8</v>
+      </c>
+      <c r="E16">
         <v>3</v>
       </c>
-      <c r="F10" s="1">
-        <v>500</v>
-      </c>
-      <c r="G10" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B11" s="1">
-        <v>6</v>
-      </c>
-      <c r="C11" s="1">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1">
-        <v>4.25</v>
-      </c>
-      <c r="E11" s="1">
-        <v>1</v>
-      </c>
-      <c r="F11" s="1">
-        <v>1600</v>
-      </c>
-      <c r="G11" s="1">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B12" s="1">
-        <v>6</v>
-      </c>
-      <c r="C12" s="1">
-        <v>2</v>
-      </c>
-      <c r="D12" s="1">
-        <v>4.25</v>
-      </c>
-      <c r="E12" s="1">
-        <v>2</v>
-      </c>
-      <c r="F12" s="1">
-        <v>1600</v>
-      </c>
-      <c r="G12" s="1">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B13" s="1">
-        <v>6</v>
-      </c>
-      <c r="C13" s="1">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>4.25</v>
-      </c>
-      <c r="E13" s="1">
-        <v>3</v>
-      </c>
-      <c r="F13" s="1">
-        <v>1600</v>
-      </c>
-      <c r="G13" s="1">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B14" s="1">
-        <v>6</v>
-      </c>
-      <c r="C14" s="1">
-        <v>2</v>
-      </c>
-      <c r="D14" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1</v>
-      </c>
-      <c r="F14" s="1">
+      <c r="F16">
         <v>4000</v>
       </c>
-      <c r="G14" s="1">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="1">
-        <v>6</v>
-      </c>
-      <c r="C15" s="1">
-        <v>2</v>
-      </c>
-      <c r="D15" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="E15" s="1">
-        <v>2</v>
-      </c>
-      <c r="F15" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G15" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="1" t="s">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1">
-        <v>6</v>
-      </c>
-      <c r="C16" s="1">
-        <v>2</v>
-      </c>
-      <c r="D16" s="1">
-        <v>6.8</v>
-      </c>
-      <c r="E16" s="1">
-        <v>3</v>
-      </c>
-      <c r="F16" s="1">
-        <v>4000</v>
-      </c>
-      <c r="G16" s="1">
+      <c r="G16">
         <v>16</v>
       </c>
     </row>

--- a/Cell data Sara DU145/2026_03_11/2026_03_11.xlsx
+++ b/Cell data Sara DU145/2026_03_11/2026_03_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{673814F5-82B8-46A4-9D59-6D2AE46EFE55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0022E705-2467-4EA9-B4D0-FCE2CC8D0DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,9 +39,6 @@
     <t>Cells plated</t>
   </si>
   <si>
-    <t>X-ray</t>
-  </si>
-  <si>
     <t>Rad</t>
   </si>
   <si>
@@ -49,6 +46,9 @@
   </si>
   <si>
     <t>Count</t>
+  </si>
+  <si>
+    <t>X</t>
   </si>
 </sst>
 </file>
@@ -860,7 +860,7 @@
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -872,18 +872,18 @@
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
       </c>
       <c r="G1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B2">
         <v>6</v>
@@ -906,7 +906,7 @@
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B3">
         <v>6</v>
@@ -929,7 +929,7 @@
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B4">
         <v>6</v>
@@ -952,7 +952,7 @@
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B5">
         <v>6</v>
@@ -975,7 +975,7 @@
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B6">
         <v>6</v>
@@ -998,7 +998,7 @@
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B7">
         <v>6</v>
@@ -1021,7 +1021,7 @@
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B8">
         <v>6</v>
@@ -1044,7 +1044,7 @@
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B9">
         <v>6</v>
@@ -1067,7 +1067,7 @@
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B10">
         <v>6</v>
@@ -1090,7 +1090,7 @@
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -1113,7 +1113,7 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1136,7 +1136,7 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B13">
         <v>6</v>
@@ -1159,7 +1159,7 @@
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14">
         <v>6</v>
@@ -1182,7 +1182,7 @@
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B15">
         <v>6</v>
@@ -1205,7 +1205,7 @@
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B16">
         <v>6</v>

--- a/Cell data Sara DU145/2026_03_11/2026_03_11.xlsx
+++ b/Cell data Sara DU145/2026_03_11/2026_03_11.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bhaan\Documents\#Master Degree\Thesis\Thesis_project\Cell data Sara DU145\2026_03_11\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0022E705-2467-4EA9-B4D0-FCE2CC8D0DF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A89A9D6-3834-4800-BC29-47F00F6A07D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1030,7 +1030,7 @@
         <v>2</v>
       </c>
       <c r="D8">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -1053,7 +1053,7 @@
         <v>2</v>
       </c>
       <c r="D9">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>2</v>
@@ -1076,7 +1076,7 @@
         <v>2</v>
       </c>
       <c r="D10">
-        <v>1.7</v>
+        <v>2</v>
       </c>
       <c r="E10">
         <v>3</v>
@@ -1099,7 +1099,7 @@
         <v>2</v>
       </c>
       <c r="D11">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E11">
         <v>1</v>
@@ -1122,7 +1122,7 @@
         <v>2</v>
       </c>
       <c r="D12">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E12">
         <v>2</v>
@@ -1145,7 +1145,7 @@
         <v>2</v>
       </c>
       <c r="D13">
-        <v>4.25</v>
+        <v>5</v>
       </c>
       <c r="E13">
         <v>3</v>
@@ -1168,7 +1168,7 @@
         <v>2</v>
       </c>
       <c r="D14">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E14">
         <v>1</v>
@@ -1191,7 +1191,7 @@
         <v>2</v>
       </c>
       <c r="D15">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E15">
         <v>2</v>
@@ -1214,7 +1214,7 @@
         <v>2</v>
       </c>
       <c r="D16">
-        <v>6.8</v>
+        <v>8</v>
       </c>
       <c r="E16">
         <v>3</v>
